--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="price_registry" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="price_registry" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Работа бетононасоса (верхний уровень: 2-й этаж+) (ВРЕМЕННО - среднее по проектам)</t>
+          <t>Работа бетононасоса (по умолчанию 36м, правится вручную)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1725,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>39833</v>
+        <v>37000</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ВРЕМЕННО 2026-08-08: верхний уровень (2-й этаж и выше) - реально используется насос БОЛЬШЕГО размера, чем на фундаменте/1-м этаже (см. concrete_pump_32m_shift). ТРЦ='36м'=39500, АРК='40м'(плита перекрытия)=42000, ЮСВ='32м+гаситель'=38000 (не различает уровни) -&gt; среднее (39500+42000+38000)/3=39833.33, округлено до 39833. Новый registry_code, добавлен вместе с fixed 2026-08-08 разделением concrete_pump_32m_shift по разделам (было общее на все 3 раздела).</t>
+          <t>ИСПРАВЛЕНО 2026-08-12: Елена подтвердила - размер/цена насоса не зависит от этажа/высоты заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты объекта - всегда ручная правка по месту, как и цена бетона. Дефолт 37000 = середина её диапазона 36000-38000 для насоса 36м. Прежняя версия (28-36м у ТРЦ / 36-40м у АРК = 'уровень определяет размер') была ошибочной гипотезой по совпадению, не подтверждённым правилом.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Работа бетононасоса (нижний уровень: фундамент/1-й этаж) (ВРЕМЕННО - среднее по проектам)</t>
+          <t>Работа бетононасоса (по умолчанию 36м, правится вручную)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2341,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>37500</v>
+        <v>37000</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ВРЕМЕННО 2026-08-08: плита 1-го этажа заливается с той же высоты, что и фундамент - в ТРЦ и АРК используется насос того же (меньшего) размера, что для фундамента (см. concrete_pump_32m_shift). Та же группа проектных значений: ТРЦ='28м'=36500, АРК='36м'=38000, ЮСВ='32м+гаситель'=38000 -&gt; среднее 37500. Новый registry_code, добавлен вместе с fixed 2026-08-08 разделением concrete_pump_32m_shift по разделам (было общее на все 3 раздела: foundation_slab/floor_slab_1/floor_slab_2).</t>
+          <t>ИСПРАВЛЕНО 2026-08-12: Елена подтвердила - размер/цена насоса не зависит от этажа/высоты заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты объекта - всегда ручная правка по месту, как и цена бетона. Дефолт 37000 = середина её диапазона 36000-38000 для насоса 36м. Прежняя версия (28-36м у ТРЦ / 36-40м у АРК = 'уровень определяет размер') была ошибочной гипотезой по совпадению, не подтверждённым правилом.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Работа бетононасоса (нижний уровень: фундамент/1-й этаж) (ВРЕМЕННО - среднее по проектам)</t>
+          <t>Работа бетононасоса (по умолчанию 36м, правится вручную)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3886,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>37500</v>
+        <v>37000</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ВРЕМЕННО 2026-08-08: нашли реальную систему - размер/цена насоса зависит от высоты заливки, не от проекта. В ТРЦ и АРК фундамент+1й этаж используют насос МЕНЬШЕГО размера, чем 2й этаж+ (см. concrete_pump_32m_shift_floor_slab_2). ЮСВ не различает уровни (один насос везде) - закономерность реальная, но не универсальная. Нижний уровень: ТРЦ='28м'=36500, АРК='36м'(фундамент)=38000, ЮСВ='32м+гаситель'=38000 -&gt; среднее (36500+38000+38000)/3=37500. Раньше этот же код делился между foundation_slab/floor_slab_1/floor_slab_2 - теперь у каждого раздела свой code, см. floor_slab_1/floor_slab_2 контракты.</t>
+          <t>ИСПРАВЛЕНО 2026-08-12: Елена подтвердила - размер/цена насоса не зависит от этажа/высоты заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты объекта - всегда ручная правка по месту, как и цена бетона. Дефолт 37000 = середина её диапазона 36000-38000 для насоса 36м. Прежняя версия (28-36м у ТРЦ / 36-40м у АРК = 'уровень определяет размер') была ошибочной гипотезой по совпадению, не подтверждённым правилом.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,6 +512,7 @@
           <t>Источник: первый лист нового прайса, строка 3. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -537,7 +538,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -545,6 +546,7 @@
           <t>Источник: первый лист нового прайса, строка 4. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -570,7 +572,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -610,7 +612,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -648,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -718,12 +720,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 200 руб./м3 из ТРЦ (лист 'НС 29.06.26', строка 32), но это была ЛЕВАЯ/белая (клиентская) колонка. Правая/серая (реальная внутренняя себестоимость) колонка для этой же строки = 0. См. подробное объяснение серая/белая структура в комментарии к timber_formwork_installation_work_m2 выше - тот же класс ошибки. Пользователь подтвердила 2026-08-06: 0 верно, работа не тарифицируется отдельно внутри.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 200 руб./м3 из реальной сметы (лист 'НС 29.06.26', строка 32), но это была ЛЕВАЯ/белая (клиентская) колонка. Правая/серая (реальная внутренняя себестоимость) колонка для этой же строки = 0. См. подробное объяснение серая/белая структура в комментарии к timber_formwork_installation_work_m2 выше - тот же класс ошибки. Пользователь подтвердила 2026-08-06: 0 верно, работа не тарифицируется отдельно внутри.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -756,12 +758,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-08: старое значение 1000 руб./м3 было непроверенным плейсхолдером (то же 'требуется проверка Елены' что и у formwork_consumables_m2). Реальная цена - в прайсе Елены на листе 'Бетон + песок' (строки 15-24), это ЗОНОВАЯ матрица по Москве и поставщикам: большинство зон (Евгений зоны 2-4, Алексей, Олег) = 1300 руб./м3 (20м3 машина), зона 1 (Евгений) = 1400 руб./м3. Взяла 1400 - это ровно та цена, что в реальной смете ТРЦ (строка 'Песок строительный' = 1400 руб./м3). Зонозависимость этот механизм не поддерживает - если у нового проекта другая зона/поставщик, значение нужно поправить здесь вручную, автоматически не подтянется.</t>
+          <t>ИСПРАВЛЕНО 2026-08-08: старое значение 1000 руб./м3 было непроверенным плейсхолдером (то же 'требуется проверка Елены' что и у formwork_consumables_m2). Реальная цена - в прайсе Елены на листе 'Бетон + песок' (строки 15-24), это ЗОНОВАЯ матрица по Москве и поставщикам: большинство зон (Евгений зоны 2-4, Алексей, Олег) = 1300 руб./м3 (20м3 машина), зона 1 (Евгений) = 1400 руб./м3. Взяла 1400 - это ровно та цена, что в одной из реальных смет (строка 'Песок строительный' = 1400 руб./м3). Зонозависимость этот механизм не поддерживает - если у нового проекта другая зона/поставщик, значение нужно поправить здесь вручную, автоматически не подтянется.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -794,12 +796,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: у 'Экскаватор-погрузчик JCB...' на первом листе прайса Елены только ОДНА цена (3500 руб./смена) - это цена РАБОТЫ (оператор), уже верно замаплена на excavator_jcb_shift. Материальной/арендной части (стоимость самого экскаватора) на первом листе нет вообще. Реальная ставка 26000 руб./смена подтверждена в 8+ независимых снимках реальных смет за несколько месяцев: ТРЦ (2026-06-29), АРК (2026-04-27), и ЮСВ на 8 разных листах/датах с 2026-02-19 по 2026-04-06 - везде одна и та же пара 26000 материал / 3500 работа для строки 'Механизированная разработка грунта, Экскаватор JCB'. До этой правки контракт (excavator_material_unit_price) ошибочно указывал на тот же registry_code, что и работа (excavator_jcb_shift), поэтому материал всегда дублировал цену работы (3500 вместо 26000).</t>
+          <t>Добавлено 2026-08-07: у 'Экскаватор-погрузчик JCB...' на первом листе прайса Елены только ОДНА цена (3500 руб./смена) - это цена РАБОТЫ (оператор), уже верно замаплена на excavator_jcb_shift. Материальной/арендной части (стоимость самого экскаватора) на первом листе нет вообще. Реальная ставка 26000 руб./смена подтверждена в 8+ независимых снимках реальных смет за несколько месяцев на всех 3 реальных проектах (снимки с 2026-02-19 по 2026-06-29, включая 8 разных листов/дат в одном из них) - везде одна и та же пара 26000 материал / 3500 работа для строки 'Механизированная разработка грунта, Экскаватор JCB'. До этой правки контракт (excavator_material_unit_price) ошибочно указывал на тот же registry_code, что и работа (excavator_jcb_shift), поэтому материал всегда дублировал цену работы (3500 вместо 26000).</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -832,12 +834,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-08: старое значение 21499.997319 не было ошибкой по сути (подтверждено по смете АРК - там та же позиция 21500 руб./м3), но само число было 'Добавлено из калькулятора MVP' - какой-то старый расчёт цена_доски/объём_доски, никогда не бывшее настоящей строкой прайса, с некрасивым хвостом из 6 знаков после запятой. Округлила до чистых 21500 - число то же самое по сути, просто без мусора.</t>
+          <t>ИСПРАВЛЕНО 2026-08-08: старое значение 21499.997319 не было ошибкой по сути (подтверждено по одной из реальных смет - там та же позиция 21500 руб./м3), но само число было 'Добавлено из калькулятора MVP' - какой-то старый расчёт цена_доски/объём_доски, никогда не бывшее настоящей строкой прайса, с некрасивым хвостом из 6 знаков после запятой. Округлила до чистых 21500 - число то же самое по сути, просто без мусора.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -870,7 +872,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -910,7 +912,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -948,7 +950,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -986,7 +988,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1024,7 +1026,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1729,12 +1731,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-12: Елена подтвердила - размер/цена насоса не зависит от этажа/высоты заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты объекта - всегда ручная правка по месту, как и цена бетона. Дефолт 37000 = середина её диапазона 36000-38000 для насоса 36м. Прежняя версия (28-36м у ТРЦ / 36-40м у АРК = 'уровень определяет размер') была ошибочной гипотезой по совпадению, не подтверждённым правилом.</t>
+          <t>ИСПРАВЛЕНО 2026-08-12: см. concrete_pump_32m_shift - Елена подтвердила, что размер/цена насоса НЕ зависит от этажа/уровня заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты - это всегда ручная правка по месту. Дефолт 37000 (середина её диапазона 36000-38000) - тот же, что у остальных 2 pump-кодов, никакой 'верхний уровень дороже' логики больше нет.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2037,7 +2039,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2077,7 +2079,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2115,7 +2117,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2345,12 +2347,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-12: Елена подтвердила - размер/цена насоса не зависит от этажа/высоты заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты объекта - всегда ручная правка по месту, как и цена бетона. Дефолт 37000 = середина её диапазона 36000-38000 для насоса 36м. Прежняя версия (28-36м у ТРЦ / 36-40м у АРК = 'уровень определяет размер') была ошибочной гипотезой по совпадению, не подтверждённым правилом.</t>
+          <t>ИСПРАВЛЕНО 2026-08-12: см. concrete_pump_32m_shift - Елена подтвердила, что размер/цена насоса НЕ зависит от этажа/уровня заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты - это всегда ручная правка по месту. Дефолт 37000 (середина её диапазона 36000-38000) - тот же, что у остальных 2 pump-кодов, никакой 'нижний уровень дешевле' логики больше нет.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2383,7 +2385,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3630,7 +3632,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3668,12 +3670,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 580 руб./м2 из ТРЦ (лист 'НС 29.06.26', строка 42), но это была ЛЕВАЯ/белая (клиентская) колонка сметы. У каждой строки в реальных сметах два параллельных блока колонок - левый (белый, с накруткой для клиента) и правый (серый, настоящая внутренняя себестоимость Елены; в ТРЦ правый блок физически закрашен заливкой, в АРК/ЮСВ заливки нет, но структура та же и подтверждается арифметикой - левое/правое = Коэф-т Рентабельности листа, обычно 1.32). Правая/серая колонка для этой строки = 0 в ТРЦ. Пользователь подтвердила 2026-08-06: 0 - это реальный ответ, эта работа у Елены отдельно не тарифицируется внутри (входит в другую работу/бригадо-день), клиенту просто показывается отдельной строкой для формы.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 580 руб./м2 из реальной сметы (лист 'НС 29.06.26', строка 42), но это была ЛЕВАЯ/белая (клиентская) колонка сметы. У каждой строки в реальных сметах два параллельных блока колонок - левый (белый, с накруткой для клиента) и правый (серый, настоящая внутренняя себестоимость Елены; в этом проекте правый блок физически закрашен заливкой, в двух других реальных проектах заливки нет, но структура та же и подтверждается арифметикой - левое/правое = Коэф-т Рентабельности листа, обычно 1.32). Правая/серая колонка для этой строки = 0 в этой смете. Пользователь подтвердила 2026-08-06: 0 - это реальный ответ, эта работа у Елены отдельно не тарифицируется внутри (входит в другую работу/бригадо-день), клиенту просто показывается отдельной строкой для формы.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -3706,12 +3708,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 120 руб./м2 из АРК/ЮСВ (левая/белая колонка на нескольких строках 'Демонтаж опалубки после завершения бетонирования'). Проверила правую/серую колонку в АРК на тех же строках - везде 0. Тот же класс ошибки, что и timber_formwork_installation_work_m2/sand_manual_moving_m3 (см. их комментарии). Пользователь подтвердила 2026-08-06: 0 верно.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 120 руб./м2 из двух реальных проектов (левая/белая колонка на нескольких строках 'Демонтаж опалубки после завершения бетонирования'). Проверила правую/серую колонку в одном из них на тех же строках - везде 0. Тот же класс ошибки, что и timber_formwork_installation_work_m2/sand_manual_moving_m3 (см. их комментарии). Пользователь подтвердила 2026-08-06: 0 верно.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -3776,12 +3778,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-07: старое значение 9759.08 руб./м2 было непроверенным плейсхолдером (см. formwork_consumables_m2 в OBSOLETE_PREVIOUS_PRICE_CODES) - в 207 раз больше реальной цены, раздувало 'Расходные материалы для установки опалубки' на floor_slab_1/floor_slab_2 до ~1.2М/730К руб. на реальном проекте ТРЦ. Реальная ставка 47 руб./м2 подтверждена на 6 строках в 2 независимых проектах: ТРЦ (5556/118.218=47.0, 1404/29.875=47.0, 4307/91.6292=47.0, 1105/23.5=47.0) и АРК (15098/321.24=47.0, 4573/97.3=47.0) - везде площадь монтажа опалубки берётся из соседней строки того же раздела сметы.</t>
+          <t>ИСПРАВЛЕНО 2026-08-07: старое значение 9759.08 руб./м2 было непроверенным плейсхолдером (см. formwork_consumables_m2 в OBSOLETE_PREVIOUS_PRICE_CODES) - в 207 раз больше реальной цены, раздувало 'Расходные материалы для установки опалубки' на floor_slab_1/floor_slab_2 до ~1.2М/730К руб. на реальном проекте. Реальная ставка 47 руб./м2 подтверждена на 6 строках в 2 независимых проектах: один проект (5556/118.218=47.0, 1404/29.875=47.0, 4307/91.6292=47.0, 1105/23.5=47.0) и другой (15098/321.24=47.0, 4573/97.3=47.0) - везде площадь монтажа опалубки берётся из соседней строки того же раздела сметы.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -3814,12 +3816,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ВРЕМЕННО 2026-08-08: цена бетона зонозависима (актуальный прайс Елены даёт зоны 6150-7690 руб./м3), готового зонного механизма пока нет. Взято простое среднее по 2 реальным проектам: ТРЦ=6600, АРК=5950 -&gt; (6600+5950)/2=6275. Заменить, когда появится зонная логика или прямое указание, в какой зоне проект.</t>
+          <t>ВРЕМЕННО 2026-08-08: цена бетона зонозависима (актуальный прайс Елены даёт зоны 6150-7690 руб./м3), готового зонного механизма пока нет. Взято простое среднее по 2 реальным проектам: 6600 и 5950 -&gt; (6600+5950)/2=6275. Заменить, когда появится зонная логика или прямое указание, в какой зоне проект.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -3852,12 +3854,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ВРЕМЕННО 2026-08-08: та же зонозависимость, что у concrete_b22_5_m3. Актуальный прайс Елены даёт цену доставки ЗА М3 (не за рейс, единицы не совпадают с этим price_code), поэтому усреднила напрямую реальные рейсовые цены из 2 проектов: ТРЦ=7200, АРК=5250 -&gt; (7200+5250)/2=6225. Заменить, когда появится зонная логика.</t>
+          <t>ВРЕМЕННО 2026-08-08: та же зонозависимость, что у concrete_b22_5_m3. Актуальный прайс Елены даёт цену доставки ЗА М3 (не за рейс, единицы не совпадают с этим price_code), поэтому усреднила напрямую реальные рейсовые цены из 2 проектов: 7200 и 5250 -&gt; (7200+5250)/2=6225. Заменить, когда появится зонная логика.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -3890,12 +3892,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-12: Елена подтвердила - размер/цена насоса не зависит от этажа/высоты заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты объекта - всегда ручная правка по месту, как и цена бетона. Дефолт 37000 = середина её диапазона 36000-38000 для насоса 36м. Прежняя версия (28-36м у ТРЦ / 36-40м у АРК = 'уровень определяет размер') была ошибочной гипотезой по совпадению, не подтверждённым правилом.</t>
+          <t>ИСПРАВЛЕНО 2026-08-12: раньше здесь была гипотеза 'размер насоса зависит от высоты этажа' (28-36м у одного реального проекта, 36-40м у другого) - это оказалось совпадением, не правилом. Елена лично подтвердила 2026-08-12: закономерности нет, слишком много факторов (расстояние от стоянки насоса до дальнего угла дома, высота), это всегда ручная правка - как и цена бетона. Её прямая рекомендация: закладывать по умолчанию 36м насос, 36000-38000р, дальше править руками под конкретный проект. Взято среднее её диапазона = 37000. Тот же дефолт теперь во всех 3 pump-кодах (см. floor_slab_1/floor_slab_2 ниже) - раздельные коды оставлены только чтобы каждую заливку можно было override-ить независимо, а не потому что уровень определяет цену.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -3928,7 +3930,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -3966,7 +3968,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4004,7 +4006,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4042,7 +4044,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4080,7 +4082,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4118,7 +4120,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4156,7 +4158,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4194,12 +4196,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: новый прайс Елены содержит одну универсальную строку 'Устройство и монтаж термовкладыша' = 100 руб./мп. В реальных эталонных сметах АРК/ТРЦ/ЮСВ работа термовставок также считается по длине с этой ставкой; для production-раздельного режима 50/100 нужен отдельный price_code, поэтому цена размножена из той же универсальной строки прайса.</t>
+          <t>Добавлено 2026-08-07: новый прайс Елены содержит одну универсальную строку 'Устройство и монтаж термовкладыша' = 100 руб./мп. Во всех 3 реальных эталонных сметах работа термовставок также считается по длине с этой ставкой; для production-раздельного режима 50/100 нужен отдельный price_code, поэтому цена размножена из той же универсальной строки прайса.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4232,7 +4234,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4270,7 +4272,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4308,7 +4310,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4586,7 +4588,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4624,7 +4626,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5080,7 +5082,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5651,7 +5653,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -5689,7 +5691,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -5727,7 +5729,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -5767,7 +5769,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -5805,7 +5807,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -5843,7 +5845,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -5883,7 +5885,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -5921,7 +5923,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -5959,7 +5961,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -5997,7 +5999,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6035,7 +6037,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6073,7 +6075,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6111,7 +6113,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6149,7 +6151,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6187,12 +6189,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07 по сверке АРК/ТРЦ/ЮСВ: в эталонных сметах это платная работа в правой части себестоимости. Временная production-ставка 250 руб./мп до отдельного подтверждения Елены.</t>
+          <t>Добавлено 2026-08-07 по сверке всех 3 реальных проектов: в эталонных сметах это платная работа в правой части себестоимости. Временная production-ставка 250 руб./мп до отдельного подтверждения Елены.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -6225,7 +6227,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6295,7 +6297,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6333,12 +6335,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: такая же цена, как у обычной V-RP мембраны (1146.91 руб./рул, прайс Елены лист 'Утеплителипленкимастика (Олег)' строка 29 - в прайсе V-GR и V-RP указаны с одинаковой ценой). Пользователь вписывал эту цену вручную в гугл-таблицу 2026-08-06 после того, как для ТРЦ впервые понадобилась V-GR (эксплуатируемая зона кровли) - перенесено в реестр, чтобы не терялось при пересборке.</t>
+          <t>Добавлено 2026-08-06: такая же цена, как у обычной V-RP мембраны (1146.91 руб./рул, прайс Елены лист 'Утеплителипленкимастика (Олег)' строка 29 - в прайсе V-GR и V-RP указаны с одинаковой ценой). Пользователь вписывал эту цену вручную в гугл-таблицу 2026-08-06 после того, как для одного из реальных проектов впервые понадобилась V-GR (эксплуатируемая зона кровли) - перенесено в реестр, чтобы не терялось при пересборке.</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -6846,7 +6848,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -6884,7 +6886,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -6922,7 +6924,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -6960,7 +6962,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -6998,7 +7000,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7036,7 +7038,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7074,7 +7076,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7308,12 +7310,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: было ошибочно затёрто на 2500 через устаревшее правило MANUAL_WORK_PRICE_CODES, которое мапило комбинированную строку 'Доставка+разгрузка' (2500) на этот материальный код - двойной счёт с schiedel_delivery_unloading_work. Реальное значение 15000 подтверждено на листе ЮСВ 'АЛ 06.04 КР1,КР2 (ЕЧ) (ЮВ)', строка 235 'Доставка вентканалов': материал=15000, работа=2500 - оба параллельных блока колонок (левый/белый и правый/серый) сходятся на этой цифре, без разночтений.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: было ошибочно затёрто на 2500 через устаревшее правило MANUAL_WORK_PRICE_CODES, которое мапило комбинированную строку 'Доставка+разгрузка' (2500) на этот материальный код - двойной счёт с schiedel_delivery_unloading_work. Реальное значение 15000 подтверждено на листе реальной сметы 'АЛ 06.04 КР1,КР2 (ЕЧ) (ЮВ)', строка 235 'Доставка вентканалов': материал=15000, работа=2500 - оба параллельных блока колонок (левый/белый и правый/серый) сходятся на этой цифре, без разночтений.</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -7346,12 +7348,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: этой строки нет в прайсе Елены отдельно (там доставка+разгрузка одной строкой = 2500) - ставка взята из реальной сметы ЮСВ, где разгрузка вручную идет отдельной строкой от доставки и стабильно равна 2500 руб./маш независимо от цены самой доставки (проверено в 2 разных листах ЮСВ: 2500/2500 и 15000/2500). По решению пользователя 2026-08-06 материал и работа считаются раздельно как более универсальный подход, а не совмещенной строкой как в АРК.</t>
+          <t>Добавлено 2026-08-06: этой строки нет в прайсе Елены отдельно (там доставка+разгрузка одной строкой = 2500) - ставка взята из реальной сметы одного из проектов, где разгрузка вручную идет отдельной строкой от доставки и стабильно равна 2500 руб./маш независимо от цены самой доставки (проверено в 2 разных листах этой сметы: 2500/2500 и 15000/2500). По решению пользователя 2026-08-06 материал и работа считаются раздельно как более универсальный подход, а не совмещенной строкой как в другом реальном проекте.</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -7384,7 +7386,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7422,7 +7424,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7460,7 +7462,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -7500,7 +7502,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -7508,120 +7510,7 @@
           <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Работы</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Гидроизоляция поверхности под первый ряд блоков, материал</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>1</v>
-      </c>
-      <c r="E220" t="n">
-        <v>250</v>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Добавлено 2026-08-09: material_unit_price ошибочно делил один registry_code с work_unit_price (cutoff_waterproofing_under_blocks_m2=100), из-за чего материал был занижен. Реальная цена материала подтверждена на ТРЦ и АРК (оба проекта: мат=250, работа=100, серый/реальный столбец) - см. отчёт 04_load_bearing_walls_lintels.md.</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>cutoff_waterproofing_material_m2</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Работы</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Технический надзор (стены/перемычки)</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>1</v>
-      </c>
-      <c r="E221" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Добавлено 2026-08-09: technical_supervision_amount ошибочно делил один registry_code (technical_supervision_fixed=5000) со строкой из раздела плиты фундамента. Реальная цена для раздела стен/перемычек подтверждена на ТРЦ (серый/реальный столбец) = 10000 - см. отчёт 04_load_bearing_walls_lintels.md.</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>technical_supervision_walls_lintels</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Работы</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой более 250мм)</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>1</v>
-      </c>
-      <c r="E222" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Добавлено 2026-08-09: строка 29 первого листа нового прайса Елены существовала, но никогда не была сопоставлена ни с одним price_code (калькулятор её не запрашивал - до 2026-07-28 было решено считать все балки одной ставкой по длине, без деления по высоте). Реальные ТРЦ и АРК смет обе делят балки по высоте с разными ставками и единицами (мп/м3) - см. reports/trc_vs_original_comparison/05_floor_slab_1.md. Подтверждено 2026-08-09.</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>beam_concrete_placing_work_m3</t>
-        </is>
-      </c>
+      <c r="H219" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,6 @@
           <t>Источник: первый лист нового прайса, строка 3. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -546,7 +545,6 @@
           <t>Источник: первый лист нового прайса, строка 4. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7510,7 +7508,82 @@
           <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой более 250мм)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Источник: первый лист прайса Елены (price_registry_elena_2026-07-28.xlsx), строка 29. Ранее исключалась по решению Елены от 2026-07-30 (единая ставка по м.п.); решение пересмотрено 2026-08-09 (подтверждено на 2 реальных проектах, балки делятся по высоте) и повторно подтверждено 2026-08-15 - балки делим, эта строка снова активна. price_code: beam_concrete_placing_work_m3.</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>beam_concrete_placing_work_m3</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Гидроизоляция отсечная, битумсодержащая типа ТЕХНОНИКОЛЬ master, материал</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>250</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>В сыром прайс-листе Елены (ни "Прайс по видам работ", ни "Утеплителипленкимастика") этого материала нет - только работа (100р/м2) там есть отдельно. Цена 250р/м2 взята напрямую из серых/внутренних колонок 2 реальных сданных смет: ТРЦ ("НС 29.06.26", строка 88, 28.4075м2) и АРК ("ЕЧ точный 27.04.26", строка 140, 35.3855м2 + строка 322 перегородки 7.83м2) - оба проекта дают идентичную цифру 250р/м2. ЮСВ не даёт отдельной цифры материала в имеющемся файле (только 100р/м2 работы, без материального разреза) - не противоречит, просто нет данных. Материал по PDF во всех 3 проектах: Гидроизоляция отсечная, битумсодержащая типа ТЕХНОНИКОЛЬ master, СТО 72746455-3.1.23-2017.</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>cutoff_waterproofing_material_m2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Бетонирование монолитной плиты перекрытия бетоном марки В22,5 (М300)</t>
+          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой более 250мм)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2033,21 +2033,21 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 29. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>concrete_placing_work_m3</t>
+          <t>beam_concrete_placing_work_m3</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Перенос, подъем бетона вручную</t>
+          <t>Бетонирование монолитной плиты перекрытия бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2070,24 +2070,22 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>5 000</t>
-        </is>
+      <c r="E52" t="n">
+        <v>12000</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>manual_concrete_lifting_m3</t>
+          <t>concrete_placing_work_m3</t>
         </is>
       </c>
     </row>
@@ -2099,65 +2097,73 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой до 250мм)</t>
+          <t>Перенос, подъем бетона вручную</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
-      <c r="E53" t="n">
-        <v>1500</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>beam_concrete_placing_work_m</t>
+          <t>manual_concrete_lifting_m3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Подача опалубки, арматуры автокраном</t>
+          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой до 250мм)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>30000.000000</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>crane_shift</t>
+          <t>beam_concrete_placing_work_m</t>
         </is>
       </c>
     </row>
@@ -2169,17 +2175,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Экструдированный пенополистирол Пеноплэкс Основа 100х585х1185 мм</t>
+          <t>Подача опалубки, арматуры автокраном</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>9020.000000</t>
+          <t>30000.000000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2189,7 +2195,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>eps_penoplex_osnova_100_m3</t>
+          <t>crane_shift</t>
         </is>
       </c>
     </row>
@@ -2201,17 +2207,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Доставка, вывоз опалубки манипулятором</t>
+          <t>Экструдированный пенополистирол Пеноплэкс Основа 100х585х1185 мм</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20000.000000</t>
+          <t>9020.000000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2221,7 +2227,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>formwork_delivery_truck</t>
+          <t>eps_penoplex_osnova_100_m3</t>
         </is>
       </c>
     </row>
@@ -2233,17 +2239,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Комплект опалубки (телескопические стойки, унивилки, треноги, водостойкая фанера, поперечные и продольные балки двутавровые)</t>
+          <t>Доставка, вывоз опалубки манипулятором</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>600.000000</t>
+          <t>20000.000000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2253,7 +2259,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>formwork_rental_m2</t>
+          <t>formwork_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -2265,17 +2271,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Доставка арматуры, металла</t>
+          <t>Комплект опалубки (телескопические стойки, унивилки, треноги, водостойкая фанера, поперечные и продольные балки двутавровые)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>22000.000000</t>
+          <t>600.000000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2285,7 +2291,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>metal_delivery_truck</t>
+          <t>formwork_rental_m2</t>
         </is>
       </c>
     </row>
@@ -2297,17 +2303,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Технический надзор</t>
+          <t>Доставка арматуры, металла</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5000.000000</t>
+          <t>22000.000000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2317,7 +2323,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>technical_supervision_fixed</t>
+          <t>metal_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -2329,33 +2335,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Работа бетононасоса (по умолчанию 36м, правится вручную)</t>
+          <t>Технический надзор</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="n">
-        <v>37000</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>5000.000000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-12: см. concrete_pump_32m_shift - Елена подтвердила, что размер/цена насоса НЕ зависит от этажа/уровня заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты - это всегда ручная правка по месту. Дефолт 37000 (середина её диапазона 36000-38000) - тот же, что у остальных 2 pump-кодов, никакой 'нижний уровень дешевле' логики больше нет.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>concrete_pump_32m_shift_floor_slab_1</t>
+          <t>technical_supervision_fixed</t>
         </is>
       </c>
     </row>
@@ -2367,61 +2367,71 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Пиломатериал обрезной для устройства опалубки ГОСТ (для опалубки монолитных перемычек)</t>
+          <t>Работа бетононасоса (по умолчанию 36м, правится вручную)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>21500</v>
+        <v>37000</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: та же цена, что и timber_m3 - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
+          <t>ИСПРАВЛЕНО 2026-08-12: см. concrete_pump_32m_shift - Елена подтвердила, что размер/цена насоса НЕ зависит от этажа/уровня заливки, а от расстояния стоянки насоса до дальнего угла дома и высоты - это всегда ручная правка по месту. Дефолт 37000 (середина её диапазона 36000-38000) - тот же, что у остальных 2 pump-кодов, никакой 'нижний уровень дешевле' логики больше нет.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>lintel_formwork_timber_m3</t>
+          <t>concrete_pump_32m_shift_floor_slab_1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Доска обрезная 25х100х6000мм 1-сорт ГОСТ</t>
+          <t>Пиломатериал обрезной для устройства опалубки ГОСТ (для опалубки монолитных перемычек)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>265</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>46154</v>
+        <v>21500</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Добавлено 2026-08-06: та же цена, что и timber_m3 - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>lintel_formwork_timber_m3</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2443,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Доска обрезная 25х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 25х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2442,7 +2452,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>397</v>
+        <v>265</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>46154</v>
@@ -2461,7 +2471,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 25х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2470,7 +2480,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>530</v>
+        <v>397</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>46154</v>
@@ -2489,7 +2499,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 50х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2498,7 +2508,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>795</v>
+        <v>530</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>46154</v>
@@ -2517,7 +2527,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х200х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 50х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2526,7 +2536,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1093</v>
+        <v>795</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>46154</v>
@@ -2545,7 +2555,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Брус обрезной 100х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 50х200х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2573,7 +2583,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Брус обрезной 100х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной 100х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2582,7 +2592,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1590</v>
+        <v>1093</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>46154</v>
@@ -2601,7 +2611,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Брус обрезной 150х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной 100х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2610,7 +2620,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2500</v>
+        <v>1590</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>46154</v>
@@ -2629,7 +2639,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 50х300х6000мм</t>
+          <t>Брус обрезной 150х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2638,7 +2648,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3800</v>
+        <v>2500</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>46154</v>
@@ -2657,7 +2667,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 20х90х6000мм</t>
+          <t>Доска сухая строганная 50х300х6000мм</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2666,7 +2676,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>360</v>
+        <v>3800</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>46154</v>
@@ -2685,7 +2695,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 20х140х6000мм</t>
+          <t>Доска сухая строганная 20х90х6000мм</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2694,7 +2704,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>46154</v>
@@ -2713,7 +2723,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х90х6000мм</t>
+          <t>Доска сухая строганная 20х140х6000мм</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2722,7 +2732,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>682</v>
+        <v>540</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>46154</v>
@@ -2741,7 +2751,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х140х6000мм</t>
+          <t>Доска сухая строганная 45х90х6000мм</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2750,7 +2760,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1022</v>
+        <v>682</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>46154</v>
@@ -2769,7 +2779,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х190х6000мм</t>
+          <t>Доска сухая строганная 45х140х6000мм</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2778,7 +2788,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1406</v>
+        <v>1022</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>46154</v>
@@ -2797,7 +2807,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 90х90х6000мм</t>
+          <t>Доска сухая строганная 45х190х6000мм</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2825,7 +2835,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 90х140х6000мм</t>
+          <t>Брус сухой строганный 90х90х6000мм</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2834,7 +2844,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2045</v>
+        <v>1406</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>46154</v>
@@ -2853,7 +2863,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 140х140х6000мм</t>
+          <t>Брус сухой строганный 90х140х6000мм</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2862,7 +2872,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3214</v>
+        <v>2045</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>46154</v>
@@ -2881,7 +2891,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 140х190х6000мм</t>
+          <t>Брус сухой строганный 140х140х6000мм</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2890,7 +2900,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4500</v>
+        <v>3214</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>46154</v>
@@ -2909,7 +2919,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 50х50х3000мм</t>
+          <t>Брус сухой строганный 140х190х6000мм</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2918,7 +2928,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>200</v>
+        <v>4500</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>46154</v>
@@ -2937,7 +2947,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 45х45х3000мм</t>
+          <t>Брус сухой строганный 50х50х3000мм</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2946,7 +2956,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>46154</v>
@@ -2965,7 +2975,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 40х50х3000мм</t>
+          <t>Брус сухой строганный 45х45х3000мм</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2993,7 +3003,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 25х100х6000мм 1-сорт ГОСТ</t>
+          <t>Брус сухой строганный 40х50х3000мм</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3002,7 +3012,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>310</v>
+        <v>175</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>46154</v>
@@ -3021,7 +3031,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 25х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 25х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3030,7 +3040,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>465</v>
+        <v>310</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>46154</v>
@@ -3049,7 +3059,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 50х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 25х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3058,7 +3068,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>621</v>
+        <v>465</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>46154</v>
@@ -3077,7 +3087,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием  50х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 50х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3086,7 +3096,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>931</v>
+        <v>621</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>46154</v>
@@ -3105,7 +3115,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 50х200х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием  50х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3114,7 +3124,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1281</v>
+        <v>931</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>46154</v>
@@ -3133,7 +3143,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 100х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 50х200х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3161,7 +3171,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 100х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной с антисептированием 100х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3170,7 +3180,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1863</v>
+        <v>1281</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>46154</v>
@@ -3189,7 +3199,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 150х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной с антисептированием 100х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3198,7 +3208,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2928</v>
+        <v>1863</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>46154</v>
@@ -3217,7 +3227,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 50х300х6000мм</t>
+          <t>Брус обрезной с антисептированием 150х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3226,7 +3236,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4200</v>
+        <v>2928</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>46154</v>
@@ -3245,7 +3255,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 20х90х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 50х300х6000мм</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3254,7 +3264,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>420</v>
+        <v>4200</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>46154</v>
@@ -3273,7 +3283,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 20х140х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 20х90х6000мм</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3282,7 +3292,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>620</v>
+        <v>420</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>46154</v>
@@ -3301,7 +3311,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х90х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 20х140х6000мм</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3310,7 +3320,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>772</v>
+        <v>620</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>46154</v>
@@ -3329,7 +3339,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х140х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 45х90х6000мм</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3338,7 +3348,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1159</v>
+        <v>772</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>46154</v>
@@ -3357,7 +3367,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х190х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 45х140х6000мм</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3366,7 +3376,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1593</v>
+        <v>1159</v>
       </c>
       <c r="F96" s="2" t="n">
         <v>46154</v>
@@ -3385,7 +3395,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 90х90х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 45х190х6000мм</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3413,7 +3423,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 90х140х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 90х90х6000мм</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3422,7 +3432,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2318</v>
+        <v>1593</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>46154</v>
@@ -3441,7 +3451,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 140х140х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 90х140х6000мм</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3450,7 +3460,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3642</v>
+        <v>2318</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>46154</v>
@@ -3469,7 +3479,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 140х190х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 140х140х6000мм</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3478,7 +3488,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5100</v>
+        <v>3642</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>46154</v>
@@ -3497,7 +3507,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 50х50х3000мм</t>
+          <t>Брус сухой строганный с антисептированием 140х190х6000мм</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3506,7 +3516,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>270</v>
+        <v>5100</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>46154</v>
@@ -3525,7 +3535,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 45х45х3000мм</t>
+          <t>Брус сухой строганный с антисептированием 50х50х3000мм</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3534,7 +3544,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>46154</v>
@@ -3553,7 +3563,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 40х50х3000мм</t>
+          <t>Брус сухой строганный с антисептированием 45х45х3000мм</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3581,7 +3591,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Фанера 1,52х1,52*18</t>
+          <t>Брус сухой строганный с антисептированием 40х50х3000мм</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3590,19 +3600,14 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1400</v>
+        <v>220</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>plywood_1520x1520_18mm_sheet</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
@@ -3614,83 +3619,78 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Фанера 1,52х1,52*18 (для опалубки монолитных перемычек)</t>
+          <t>Фанера 1,52х1,52*18</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
-      </c>
-      <c r="D105" t="n">
-        <v>1</v>
       </c>
       <c r="E105" t="n">
         <v>1400</v>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+      <c r="F105" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: тот же лист фанеры, что и plywood_1520x1520_18mm_sheet (прайс Елены, лист 'Пиломатериалы (Олег)', строка 23) - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>lintel_formwork_plywood_sheet</t>
+          <t>plywood_1520x1520_18mm_sheet</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Монтаж опалубки из доски для отбортовки плиты</t>
+          <t>Фанера 1,52х1,52*18 (для опалубки монолитных перемычек)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 580 руб./м2 из реальной сметы (лист 'НС 29.06.26', строка 42), но это была ЛЕВАЯ/белая (клиентская) колонка сметы. У каждой строки в реальных сметах два параллельных блока колонок - левый (белый, с накруткой для клиента) и правый (серый, настоящая внутренняя себестоимость Елены; в этом проекте правый блок физически закрашен заливкой, в двух других реальных проектах заливки нет, но структура та же и подтверждается арифметикой - левое/правое = Коэф-т Рентабельности листа, обычно 1.32). Правая/серая колонка для этой строки = 0 в этой смете. Пользователь подтвердила 2026-08-06: 0 - это реальный ответ, эта работа у Елены отдельно не тарифицируется внутри (входит в другую работу/бригадо-день), клиенту просто показывается отдельной строкой для формы.</t>
+          <t>Добавлено 2026-08-06: тот же лист фанеры, что и plywood_1520x1520_18mm_sheet (прайс Елены, лист 'Пиломатериалы (Олег)', строка 23) - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>timber_formwork_installation_work_m2</t>
+          <t>lintel_formwork_plywood_sheet</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Устройство фундаментной плиты</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Демонтаж опалубки после завершения бетонирования</t>
+          <t>Монтаж опалубки из доски для отбортовки плиты</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 120 руб./м2 из двух реальных проектов (левая/белая колонка на нескольких строках 'Демонтаж опалубки после завершения бетонирования'). Проверила правую/серую колонку в одном из них на тех же строках - везде 0. Тот же класс ошибки, что и timber_formwork_installation_work_m2/sand_manual_moving_m3 (см. их комментарии). Пользователь подтвердила 2026-08-06: 0 верно.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 580 руб./м2 из реальной сметы (лист 'НС 29.06.26', строка 42), но это была ЛЕВАЯ/белая (клиентская) колонка сметы. У каждой строки в реальных сметах два параллельных блока колонок - левый (белый, с накруткой для клиента) и правый (серый, настоящая внутренняя себестоимость Елены; в этом проекте правый блок физически закрашен заливкой, в двух других реальных проектах заливки нет, но структура та же и подтверждается арифметикой - левое/правое = Коэф-т Рентабельности листа, обычно 1.32). Правая/серая колонка для этой строки = 0 в этой смете. Пользователь подтвердила 2026-08-06: 0 - это реальный ответ, эта работа у Елены отдельно не тарифицируется внутри (входит в другую работу/бригадо-день), клиенту просто показывается отдельной строкой для формы.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>formwork_dismantling_work_m2</t>
+          <t>timber_formwork_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -3728,27 +3728,33 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовкладыша 150*400*250мм шаг 200мм</t>
+          <t>Демонтаж опалубки после завершения бетонирования</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 120 руб./м2 из двух реальных проектов (левая/белая колонка на нескольких строках 'Демонтаж опалубки после завершения бетонирования'). Проверила правую/серую колонку в одном из них на тех же строках - везде 0. Тот же класс ошибки, что и timber_formwork_installation_work_m2/sand_manual_moving_m3 (см. их комментарии). Пользователь подтвердила 2026-08-06: 0 верно.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>thermal_insert_installation_work_m</t>
+          <t>formwork_dismantling_work_m2</t>
         </is>
       </c>
     </row>
@@ -3760,33 +3766,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Расходные материалы для установки опалубки (смазка; звездочки ПВХ, трубки)</t>
+          <t>Устройство и монтаж термовкладыша 150*400*250мм шаг 200мм</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" t="n">
-        <v>47</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-07: старое значение 9759.08 руб./м2 было непроверенным плейсхолдером (см. formwork_consumables_m2 в OBSOLETE_PREVIOUS_PRICE_CODES) - в 207 раз больше реальной цены, раздувало 'Расходные материалы для установки опалубки' на floor_slab_1/floor_slab_2 до ~1.2М/730К руб. на реальном проекте. Реальная ставка 47 руб./м2 подтверждена на 6 строках в 2 независимых проектах: один проект (5556/118.218=47.0, 1404/29.875=47.0, 4307/91.6292=47.0, 1105/23.5=47.0) и другой (15098/321.24=47.0, 4573/97.3=47.0) - везде площадь монтажа опалубки берётся из соседней строки того же раздела сметы.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>formwork_consumables_m2</t>
+          <t>thermal_insert_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -3798,33 +3798,33 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Бетон марки В22,5 (М300) (ВРЕМЕННО - среднее по проектам, до внедрения зон)</t>
+          <t>Расходные материалы для установки опалубки (смазка; звездочки ПВХ, трубки)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>6275</v>
+        <v>47</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ВРЕМЕННО 2026-08-08: цена бетона зонозависима (актуальный прайс Елены даёт зоны 6150-7690 руб./м3), готового зонного механизма пока нет. Взято простое среднее по 2 реальным проектам: 6600 и 5950 -&gt; (6600+5950)/2=6275. Заменить, когда появится зонная логика или прямое указание, в какой зоне проект.</t>
+          <t>ИСПРАВЛЕНО 2026-08-07: старое значение 9759.08 руб./м2 было непроверенным плейсхолдером (см. formwork_consumables_m2 в OBSOLETE_PREVIOUS_PRICE_CODES) - в 207 раз больше реальной цены, раздувало 'Расходные материалы для установки опалубки' на floor_slab_1/floor_slab_2 до ~1.2М/730К руб. на реальном проекте. Реальная ставка 47 руб./м2 подтверждена на 6 строках в 2 независимых проектах: один проект (5556/118.218=47.0, 1404/29.875=47.0, 4307/91.6292=47.0, 1105/23.5=47.0) и другой (15098/321.24=47.0, 4573/97.3=47.0) - везде площадь монтажа опалубки берётся из соседней строки того же раздела сметы.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>concrete_b22_5_m3</t>
+          <t>formwork_consumables_m2</t>
         </is>
       </c>
     </row>
@@ -3836,33 +3836,33 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Доставка бетона до объекта (ВРЕМЕННО - среднее по проектам)</t>
+          <t>Бетон марки В22,5 (М300) (ВРЕМЕННО - среднее по проектам, до внедрения зон)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>6225</v>
+        <v>6275</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ВРЕМЕННО 2026-08-08: та же зонозависимость, что у concrete_b22_5_m3. Актуальный прайс Елены даёт цену доставки ЗА М3 (не за рейс, единицы не совпадают с этим price_code), поэтому усреднила напрямую реальные рейсовые цены из 2 проектов: 7200 и 5250 -&gt; (7200+5250)/2=6225. Заменить, когда появится зонная логика.</t>
+          <t>ВРЕМЕННО 2026-08-08: цена бетона зонозависима (актуальный прайс Елены даёт зоны 6150-7690 руб./м3), готового зонного механизма пока нет. Взято простое среднее по 2 реальным проектам: 6600 и 5950 -&gt; (6600+5950)/2=6275. Заменить, когда появится зонная логика или прямое указание, в какой зоне проект.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>concrete_delivery_trip</t>
+          <t>concrete_b22_5_m3</t>
         </is>
       </c>
     </row>
@@ -3874,83 +3874,83 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Работа бетононасоса (по умолчанию 36м, правится вручную)</t>
+          <t>Доставка бетона до объекта (ВРЕМЕННО - среднее по проектам)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>37000</v>
+        <v>6225</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-12: раньше здесь была гипотеза 'размер насоса зависит от высоты этажа' (28-36м у одного реального проекта, 36-40м у другого) - это оказалось совпадением, не правилом. Елена лично подтвердила 2026-08-12: закономерности нет, слишком много факторов (расстояние от стоянки насоса до дальнего угла дома, высота), это всегда ручная правка - как и цена бетона. Её прямая рекомендация: закладывать по умолчанию 36м насос, 36000-38000р, дальше править руками под конкретный проект. Взято среднее её диапазона = 37000. Тот же дефолт теперь во всех 3 pump-кодах (см. floor_slab_1/floor_slab_2 ниже) - раздельные коды оставлены только чтобы каждую заливку можно было override-ить независимо, а не потому что уровень определяет цену.</t>
+          <t>ВРЕМЕННО 2026-08-08: та же зонозависимость, что у concrete_b22_5_m3. Актуальный прайс Елены даёт цену доставки ЗА М3 (не за рейс, единицы не совпадают с этим price_code), поэтому усреднила напрямую реальные рейсовые цены из 2 проектов: 7200 и 5250 -&gt; (7200+5250)/2=6225. Заменить, когда появится зонная логика.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>concrete_pump_32m_shift</t>
+          <t>concrete_delivery_trip</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Гидроизоляция</t>
+          <t>Устройство фундаментной плиты</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Утепление стен ЭППС 50мм, работа</t>
+          <t>Работа бетононасоса (по умолчанию 36м, правится вручную)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D113" t="n">
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>500</v>
+        <v>37000</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-08 (ответ Елены на вопрос от 2026-08-06): это не 'один проход на оба слоя' - работа утепления не зависит от толщины плиты ЭППС, ставка за м2 одинаковая что для 50мм, что для 100мм слоя (это разные площади/конструкции, не два слоя друг на друге). Раньше стояло 0 из опасения задвоить деньги поверх ставки 100мм-слоя - опасение снято, задвоения нет, т.к. 50мм и 100мм всегда считаются по СВОИМ отдельным площадям. Ставка = eps_wall_insulation_work_m2 (500 руб./м2).</t>
+          <t>ИСПРАВЛЕНО 2026-08-12: раньше здесь была гипотеза 'размер насоса зависит от высоты этажа' (28-36м у одного реального проекта, 36-40м у другого) - это оказалось совпадением, не правилом. Елена лично подтвердила 2026-08-12: закономерности нет, слишком много факторов (расстояние от стоянки насоса до дальнего угла дома, высота), это всегда ручная правка - как и цена бетона. Её прямая рекомендация: закладывать по умолчанию 36м насос, 36000-38000р, дальше править руками под конкретный проект. Взято среднее её диапазона = 37000. Тот же дефолт теперь во всех 3 pump-кодах (см. floor_slab_1/floor_slab_2 ниже) - раздельные коды оставлены только чтобы каждую заливку можно было override-ить независимо, а не потому что уровень определяет цену.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>eps_wall_insulation_work_50_m2</t>
+          <t>concrete_pump_32m_shift</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Гидроизоляция</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Устройство утепления низа плиты</t>
+          <t>Утепление стен ЭППС 50мм, работа</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3962,21 +3962,21 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.</t>
+          <t>ИСПРАВЛЕНО 2026-08-08 (ответ Елены на вопрос от 2026-08-06): это не 'один проход на оба слоя' - работа утепления не зависит от толщины плиты ЭППС, ставка за м2 одинаковая что для 50мм, что для 100мм слоя (это разные площади/конструкции, не два слоя друг на друге). Раньше стояло 0 из опасения задвоить деньги поверх ставки 100мм-слоя - опасение снято, задвоения нет, т.к. 50мм и 100мм всегда считаются по СВОИМ отдельным площадям. Ставка = eps_wall_insulation_work_m2 (500 руб./м2).</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>eps_bottom_slab_insulation_work_m2</t>
+          <t>eps_wall_insulation_work_50_m2</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Утепление торца плиты ЭППС 100мм</t>
+          <t>Устройство утепления низа плиты</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4000,21 +4000,21 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>eps_wall_insulation_work_m2</t>
+          <t>eps_bottom_slab_insulation_work_m2</t>
         </is>
       </c>
     </row>
@@ -4026,33 +4026,33 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовкладыша</t>
+          <t>Утепление торца плиты ЭППС 100мм</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D116" t="n">
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>thermal_insert_combined_installation_work_m</t>
+          <t>eps_wall_insulation_work_m2</t>
         </is>
       </c>
     </row>
@@ -4064,33 +4064,33 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
+          <t>Устройство и монтаж термовкладыша</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>770</v>
+        <v>100</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>roof_eps_insulation_installation_work_m2</t>
+          <t>thermal_insert_combined_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -4102,33 +4102,33 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 50 мм (для термовставок)</t>
+          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D118" t="n">
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>8800</v>
+        <v>770</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 43. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>thermal_insert_50_material_m3</t>
+          <t>roof_eps_insulation_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 100 мм (для термовставок)</t>
+          <t>Пеноплэкс ГЕО 50 мм (для термовставок)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4152,21 +4152,21 @@
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 44. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 43. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>thermal_insert_100_material_m3</t>
+          <t>thermal_insert_50_material_m3</t>
         </is>
       </c>
     </row>
@@ -4178,33 +4178,33 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовставок 50 мм</t>
+          <t>Пеноплэкс ГЕО 100 мм (для термовставок)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D120" t="n">
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>100</v>
+        <v>8900</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: новый прайс Елены содержит одну универсальную строку 'Устройство и монтаж термовкладыша' = 100 руб./мп. Во всех 3 реальных эталонных сметах работа термовставок также считается по длине с этой ставкой; для production-раздельного режима 50/100 нужен отдельный price_code, поэтому цена размножена из той же универсальной строки прайса.</t>
+          <t>Источник: первый лист нового прайса, строка 44. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>thermal_insert_50_installation_work_m</t>
+          <t>thermal_insert_100_material_m3</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовставок 100 мм</t>
+          <t>Устройство и монтаж термовставок 50 мм</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4232,17 +4232,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: та же универсальная работа 'Устройство и монтаж термовкладыша' = 100 руб./мп из нового прайса Елены. Толщина слоя меняет материал, но не ставку монтажной работы по м.п.</t>
+          <t>Добавлено 2026-08-07: новый прайс Елены содержит одну универсальную строку 'Устройство и монтаж термовкладыша' = 100 руб./мп. Во всех 3 реальных эталонных сметах работа термовставок также считается по длине с этой ставкой; для production-раздельного режима 50/100 нужен отдельный price_code, поэтому цена размножена из той же универсальной строки прайса.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>thermal_insert_100_installation_work_m</t>
+          <t>thermal_insert_50_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовставок (произвольный типоразмер)</t>
+          <t>Устройство и монтаж термовставок 100 мм</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: для режима thermal_insert_mode='items' калькулятор считает одну работу по суммарной длине всех термовставок произвольных типоразмеров. Ставка берется из той же универсальной строки нового прайса Елены 'Устройство и монтаж термовкладыша' = 100 руб./мп.</t>
+          <t>Добавлено 2026-08-07: та же универсальная работа 'Устройство и монтаж термовкладыша' = 100 руб./мп из нового прайса Елены. Толщина слоя меняет материал, но не ставку монтажной работы по м.п.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>thermal_insert_items_installation_work_m</t>
+          <t>thermal_insert_100_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -4292,63 +4292,71 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Материал термовставок (произвольный типоразмер)</t>
+          <t>Устройство и монтаж термовставок (произвольный типоразмер)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D123" t="n">
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>8900</v>
+        <v>100</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: общий fallback для thermal_insert_items произвольного типоразмера. Новый прайс Елены дает Пеноплэкс ГЕО 100 мм (для термовставок) = 8900 руб./м3 и Пеноплэкс ГЕО 50 мм = 8800 руб./м3; для произвольных типоразмеров без отдельного толщинного price_code используем базовую цену 100 мм как более частый материал термовставок. Если в будущем появятся разные цены по eps_size, заменить на построчный price_code.</t>
+          <t>Добавлено 2026-08-07: для режима thermal_insert_mode='items' калькулятор считает одну работу по суммарной длине всех термовставок произвольных типоразмеров. Ставка берется из той же универсальной строки нового прайса Елены 'Устройство и монтаж термовкладыша' = 100 руб./мп.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>thermal_insert_item_material_m3</t>
+          <t>thermal_insert_items_installation_work_m</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Planter Standard Технониколь 40м2-1рул</t>
+          <t>Материал термовставок (произвольный типоразмер)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>рул</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>4738</v>
+        <v>8900</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Добавлено 2026-08-07: общий fallback для thermal_insert_items произвольного типоразмера. Новый прайс Елены дает Пеноплэкс ГЕО 100 мм (для термовставок) = 8900 руб./м3 и Пеноплэкс ГЕО 50 мм = 8800 руб./м3; для произвольных типоразмеров без отдельного толщинного price_code используем базовую цену 100 мм как более частый материал термовставок. Если в будущем появятся разные цены по eps_size, заменить на построчный price_code.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>planter_standard_roll</t>
+          <t>thermal_insert_item_material_m3</t>
         </is>
       </c>
     </row>
@@ -4360,16 +4368,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PLANTERBAND 10м х 10см-1шт</t>
+          <t>Planter Standard Технониколь 40м2-1рул</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>рул</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>750</v>
+        <v>4738</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4378,7 +4386,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>planterband_item</t>
+          <t>planter_standard_roll</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4398,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Праймер битумный AquaMast, 18 л-1шт</t>
+          <t>PLANTERBAND 10м х 10см-1шт</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4399,7 +4407,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2865</v>
+        <v>750</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4408,7 +4416,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>bitumen_primer_aquamast_18l_item</t>
+          <t>planterband_item</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4428,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
+          <t>Праймер битумный AquaMast, 18 л-1шт</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4429,7 +4437,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2828.21</v>
+        <v>2865</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4438,7 +4446,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>bitumen_mastic_aquamast_18kg_item</t>
+          <t>bitumen_primer_aquamast_18l_item</t>
         </is>
       </c>
     </row>
@@ -4450,16 +4458,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
+          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>8800</v>
+        <v>2828.21</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4468,7 +4476,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>eps_geo_50_m3</t>
+          <t>bitumen_mastic_aquamast_18kg_item</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4488,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
+          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4489,7 +4497,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -4498,7 +4506,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>eps_geo_100_m3</t>
+          <t>eps_geo_50_m3</t>
         </is>
       </c>
     </row>
@@ -4510,16 +4518,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Клей-пена для ЭППС-1шт</t>
+          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>450</v>
+        <v>8900</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4528,7 +4536,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>eps_foam_glue_can</t>
+          <t>eps_geo_100_m3</t>
         </is>
       </c>
     </row>
@@ -4540,37 +4548,37 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
+          <t>Клей-пена для ЭППС-1шт</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>109</v>
+        <v>450</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
+          <t>Обновлено 04.05</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>geotextile_dornit_300_m2</t>
+          <t>eps_foam_glue_can</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
+          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4578,25 +4586,17 @@
           <t>м2</t>
         </is>
       </c>
-      <c r="D132" t="n">
-        <v>1</v>
-      </c>
       <c r="E132" t="n">
-        <v>350</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+        <v>109</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>bitumen_waterproofing_work_m2</t>
+          <t>geotextile_dornit_300_m2</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Монтаж мембраны PLANTER стандарт</t>
+          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4620,49 +4620,59 @@
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>planter_membrane_installation_work_m2</t>
+          <t>bitumen_waterproofing_work_m2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Проволока</t>
+          <t>Монтаж мембраны PLANTER стандарт</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D134" t="n">
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>75</v>
+        <v>100</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
+          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>planter_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -4674,26 +4684,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 25 мм</t>
+          <t>Проволока</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1п.м</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.7</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>155.8</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>46214</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>rebar_a500_d25_m</t>
+        <v>75</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4712,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 20мм</t>
+          <t>Арматура класса А500 диаметром 25 мм</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4717,19 +4724,14 @@
         <v>11.7</v>
       </c>
       <c r="E136" t="n">
-        <v>100.25</v>
+        <v>155.8</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>46214</v>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
-        </is>
-      </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>rebar_a500_d20_m</t>
+          <t>rebar_a500_d25_m</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4743,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 16 мм</t>
+          <t>Арматура класса А500 диаметром 20мм</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4753,14 +4755,19 @@
         <v>11.7</v>
       </c>
       <c r="E137" t="n">
-        <v>64.90000000000001</v>
+        <v>100.25</v>
       </c>
       <c r="F137" s="2" t="n">
         <v>46214</v>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>rebar_a500_d16_m</t>
+          <t>rebar_a500_d20_m</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4779,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 12мм</t>
+          <t>Арматура класса А500 диаметром 16 мм</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4784,14 +4791,14 @@
         <v>11.7</v>
       </c>
       <c r="E138" t="n">
-        <v>36.85</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F138" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>rebar_a500_d12_m</t>
+          <t>rebar_a500_d16_m</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4810,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 10 мм</t>
+          <t>Арматура класса А500 диаметром 12мм</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4815,14 +4822,14 @@
         <v>11.7</v>
       </c>
       <c r="E139" t="n">
-        <v>27.16</v>
+        <v>36.85</v>
       </c>
       <c r="F139" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>rebar_a500_d10_m</t>
+          <t>rebar_a500_d12_m</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4841,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 8 мм</t>
+          <t>Арматура класса А500 диаметром 10 мм</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4846,14 +4853,14 @@
         <v>11.7</v>
       </c>
       <c r="E140" t="n">
-        <v>18.5</v>
+        <v>27.16</v>
       </c>
       <c r="F140" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>rebar_a240_d8_m</t>
+          <t>rebar_a500_d10_m</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4872,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 6 мм</t>
+          <t>Арматура класса А240 диаметром 8 мм</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4877,47 +4884,45 @@
         <v>11.7</v>
       </c>
       <c r="E141" t="n">
-        <v>10.25</v>
+        <v>18.5</v>
       </c>
       <c r="F141" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>rebar_a240_d6_m</t>
+          <t>rebar_a240_d8_m</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Блок D 400</t>
+          <t>Арматура класса А240 диаметром 6 мм</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>34,56 м3</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.7</v>
       </c>
       <c r="E142" t="n">
-        <v>5900</v>
+        <v>10.25</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+        <v>46214</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>rebar_a240_d6_m</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4934,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Блок D 500</t>
+          <t>Блок D 400</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4939,18 +4944,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>32,4 м3</t>
+          <t>34,56 м3</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5200</v>
+        <v>5900</v>
       </c>
       <c r="F143" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4967,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Блок D 400</t>
+          <t>Блок D 500</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4972,18 +4977,18 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1,8 м3</t>
+          <t>32,4 м3</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6300</v>
+        <v>5200</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -4995,7 +5000,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Блок D 500</t>
+          <t>Блок D 400</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5009,7 +5014,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5800</v>
+        <v>6300</v>
       </c>
       <c r="F145" s="2" t="n">
         <v>46146</v>
@@ -5028,101 +5033,102 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Блок D 500</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>1,8 м3</t>
+        </is>
       </c>
       <c r="E146" t="n">
-        <v>360</v>
+        <v>5800</v>
       </c>
       <c r="F146" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>block_adhesive_bag</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Кровля</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Воронка парапетная с листвоуловителем (материал)</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мешок 25 кг</t>
         </is>
       </c>
       <c r="D147" t="n">
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>6001.23</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+        <v>360</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: та же причина, что и у внутренней воронки - материалы не читаются автоматическим скриптом, цена взята напрямую из листа 'Утеплителипленкимастика (Олег)', строка 31 ('Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650') = 6001.23 руб./шт. До этой правки код ошибочно получал цену РАБОТЫ монтажа (5000 руб.) через устаревшее сопоставление в MANUAL_WORK_PRICE_CODES - реальная цена материала выше, это была настоящая ошибка в деньгах, не совпадение.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>roof_parapet_drain_item</t>
+          <t>block_adhesive_bag</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Доставка блоков, смеси</t>
+          <t>Воронка парапетная с листвоуловителем (материал)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>28000</t>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>6001.23</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Добавлено 2026-08-06: та же причина, что и у внутренней воронки - материалы не читаются автоматическим скриптом, цена взята напрямую из листа 'Утеплителипленкимастика (Олег)', строка 31 ('Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650') = 6001.23 руб./шт. До этой правки код ошибочно получал цену РАБОТЫ монтажа (5000 руб.) через устаревшее сопоставление в MANUAL_WORK_PRICE_CODES - реальная цена материала выше, это была настоящая ошибка в деньгах, не совпадение.</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>block_delivery_truck</t>
+          <t>roof_parapet_drain_item</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5140,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Разгрузка блоков, смеси манипулятором</t>
+          <t>Доставка блоков, смеси</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5144,7 +5150,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5154,7 +5160,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>block_unloading_manipulator_truck</t>
+          <t>block_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -5166,17 +5172,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Газобетонный блок D400 600x400x250 мм</t>
+          <t>Разгрузка блоков, смеси манипулятором</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5186,7 +5192,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>gas_block_d400_m3</t>
+          <t>block_unloading_manipulator_truck</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5204,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x150x250 мм</t>
+          <t>Газобетонный блок D400 600x400x250 мм</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5208,7 +5214,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5218,7 +5224,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>gas_block_d500_150_m3</t>
+          <t>gas_block_d400_m3</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5236,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x250x250 мм</t>
+          <t>Газобетонный блок D500 600x150x250 мм</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5240,7 +5246,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5250,7 +5256,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>gas_block_d500_m3</t>
+          <t>gas_block_d500_150_m3</t>
         </is>
       </c>
     </row>
@@ -5262,17 +5268,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Пескобетон М300 40 кг</t>
+          <t>Газобетонный блок D500 600x250x250 мм</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5282,38 +5288,39 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>sand_concrete_bag</t>
+          <t>gas_block_d500_m3</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Пескобетон М300 40 кг</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="n">
-        <v>659.77</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>46146</v>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>sand_concrete_bag</t>
         </is>
       </c>
     </row>
@@ -5325,26 +5332,26 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Сетка 5/0.4/100</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>рулон</t>
+          <t>мешок 25 кг</t>
         </is>
       </c>
       <c r="D155" t="n">
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>1304.63</v>
+        <v>659.77</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5363,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Сетка 5/0.5/100</t>
+          <t>Сетка 5/0.4/100</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5368,7 +5375,7 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>1729.38</v>
+        <v>1304.63</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>46146</v>
@@ -5387,26 +5394,26 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PTH 8</t>
+          <t>Сетка 5/0.5/100</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>рулон</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>100.62</v>
+        <v>1729.38</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5425,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PTH 12</t>
+          <t>PTH 8</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5427,17 +5434,17 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E158" t="n">
-        <v>150.62</v>
+        <v>100.62</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5456,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PTH 20</t>
+          <t>PTH 12</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5458,17 +5465,17 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E159" t="n">
-        <v>171.17</v>
+        <v>150.62</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5487,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PTH 25М</t>
+          <t>PTH 20</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5489,17 +5496,17 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E160" t="n">
-        <v>180.89</v>
+        <v>171.17</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5518,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PTH 38</t>
+          <t>PTH 25М</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5523,7 +5530,7 @@
         <v>60</v>
       </c>
       <c r="E161" t="n">
-        <v>155.66</v>
+        <v>180.89</v>
       </c>
       <c r="F161" s="2" t="n">
         <v>46146</v>
@@ -5542,7 +5549,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PTH 38 Termo</t>
+          <t>PTH 38</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5554,7 +5561,7 @@
         <v>60</v>
       </c>
       <c r="E162" t="n">
-        <v>201.14</v>
+        <v>155.66</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>46146</v>
@@ -5573,7 +5580,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PTH 44</t>
+          <t>PTH 38 Termo</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5582,17 +5589,17 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E163" t="n">
-        <v>176.58</v>
+        <v>201.14</v>
       </c>
       <c r="F163" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5611,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PTH 51</t>
+          <t>PTH 44</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5616,7 +5623,7 @@
         <v>50</v>
       </c>
       <c r="E164" t="n">
-        <v>225.53</v>
+        <v>176.58</v>
       </c>
       <c r="F164" s="2" t="n">
         <v>46146</v>
@@ -5630,38 +5637,31 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Гидроизоляция поверхности под первый ряд блоков</t>
+          <t>PTH 51</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E165" t="n">
-        <v>100</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+        <v>225.53</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>cutoff_waterproofing_under_blocks_m2</t>
+          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5673,33 +5673,33 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
+          <t>Укладка ЦСП в 2 слоя (24мм)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D166" t="n">
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 47. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>edge_insulation_work_m</t>
+          <t>roof_screed_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Укладка ЭППС 50мм под плитой</t>
+          <t>Гидроизоляция поверхности под первый ряд блоков</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5723,21 +5723,21 @@
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>eps_laying_work_m2</t>
+          <t>cutoff_waterproofing_under_blocks_m2</t>
         </is>
       </c>
     </row>
@@ -5749,35 +5749,33 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
+          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D168" t="n">
         <v>1</v>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>1 200</t>
-        </is>
+      <c r="E168" t="n">
+        <v>450</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>gas_block_cladding_work_m2</t>
+          <t>edge_insulation_work_m</t>
         </is>
       </c>
     </row>
@@ -5789,33 +5787,33 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Кладка парапета из газобетонных блоков</t>
+          <t>Укладка ЭППС 50мм под плитой</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D169" t="n">
         <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>7000</v>
+        <v>250</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>gas_block_masonry_work_m3</t>
+          <t>eps_laying_work_m2</t>
         </is>
       </c>
     </row>
@@ -5827,33 +5825,35 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
+          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D170" t="n">
         <v>1</v>
       </c>
-      <c r="E170" t="n">
-        <v>1200</v>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1 200</t>
+        </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>lintel_concreting_work_m</t>
+          <t>gas_block_cladding_work_m2</t>
         </is>
       </c>
     </row>
@@ -5865,35 +5865,33 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
+          <t>Кладка парапета из газобетонных блоков</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>1</v>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
+      <c r="E171" t="n">
+        <v>7000</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>scaffolding_setup_dismantling_work_set</t>
+          <t>gas_block_masonry_work_m3</t>
         </is>
       </c>
     </row>
@@ -5905,33 +5903,33 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Резка блока под перемычку (U-блок)</t>
+          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D172" t="n">
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>u_block_lintel_cutting_item</t>
+          <t>lintel_concreting_work_m</t>
         </is>
       </c>
     </row>
@@ -5943,33 +5941,35 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
+          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D173" t="n">
         <v>1</v>
       </c>
-      <c r="E173" t="n">
-        <v>1500</v>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>lintel_monolithic_concreting_work_m</t>
+          <t>scaffolding_setup_dismantling_work_set</t>
         </is>
       </c>
     </row>
@@ -5981,33 +5981,33 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Укладка ПВХ Мембраны</t>
+          <t>Резка блока под перемычку (U-блок)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D174" t="n">
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>630</v>
+        <v>400</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_installation_work_m2</t>
+          <t>u_block_lintel_cutting_item</t>
         </is>
       </c>
     </row>
@@ -6019,33 +6019,33 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Установка воронки парапетной</t>
+          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D175" t="n">
         <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>roof_parapet_drain_installation_item</t>
+          <t>lintel_monolithic_concreting_work_m</t>
         </is>
       </c>
     </row>
@@ -6057,33 +6057,33 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Кладка вентканалов Schiedel</t>
+          <t>Укладка ПВХ Мембраны</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D176" t="n">
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>5000</v>
+        <v>630</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>schiedel_masonry_work_m</t>
+          <t>roof_pvc_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -6095,33 +6095,33 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Блок D400 (для кладки шахты вентканалов)</t>
+          <t>Установка воронки парапетной</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D177" t="n">
         <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>6100</v>
+        <v>5000</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 45. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>schiedel_masonry_gas_block_d400_m3</t>
+          <t>roof_parapet_drain_installation_item</t>
         </is>
       </c>
     </row>
@@ -6133,33 +6133,33 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Блок D500 (для кладки шахты вентканалов)</t>
+          <t>Кладка вентканалов Schiedel</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D178" t="n">
         <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 46. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>schiedel_masonry_gas_block_d500_m3</t>
+          <t>schiedel_masonry_work_m</t>
         </is>
       </c>
     </row>
@@ -6171,33 +6171,33 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Штробление блоков под дополнительное усиление, армирование арматурой диаметром 10 мм</t>
+          <t>Блок D400 (для кладки шахты вентканалов)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D179" t="n">
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>250</v>
+        <v>6100</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07 по сверке всех 3 реальных проектов: в эталонных сметах это платная работа в правой части себестоимости. Временная production-ставка 250 руб./мп до отдельного подтверждения Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 45. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>block_chasing_reinforcement_work_m</t>
+          <t>schiedel_masonry_gas_block_d400_m3</t>
         </is>
       </c>
     </row>
@@ -6209,191 +6209,217 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
+          <t>Блок D500 (для кладки шахты вентканалов)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D180" t="n">
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>450</v>
+        <v>5400</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Добавлено по ответу Елены 2026-07-30: ставка такая же, как утепление балок и торца плиты.</t>
+          <t>Источник: первый лист нового прайса, строка 46. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>lintel_edge_insulation_work_m</t>
+          <t>schiedel_masonry_gas_block_d500_m3</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
+          <t>Штробление блоков под дополнительное усиление, армирование арматурой диаметром 10 мм</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>111.76</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>250</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+          <t>Добавлено 2026-08-07 по сверке всех 3 реальных проектов: в эталонных сметах это платная работа в правой части себестоимости. Временная production-ставка 250 руб./мп до отдельного подтверждения Елены.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>roof_geotextile_technonikol_prof_300_m2</t>
+          <t>block_chasing_reinforcement_work_m</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Воронка кровельная внутренняя с обогревом (материал)</t>
+          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>5000</v>
+        <v>450</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: материалы не читаются автоматическим скриптом (только первый лист 'Прайс по видам работ', лист с материалами 'Утеплителипленкимастика (Олег)' сюда не входит) - цена 5000 руб./шт взята оттуда напрямую, строка 32 ('Воронка кровельная (с обжимным мет. фланцем с обогревом 110х450мм)'). До этой правки код случайно получал ту же цену через устаревшее (неверное) сопоставление с работой монтажа - см. исправление в MANUAL_WORK_PRICE_CODES выше. Цена совпала случайно (обе 5000), поэтому баг был незаметен.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: ставка такая же, как утепление балок и торца плиты.</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>roof_internal_drain_with_heating_item</t>
+          <t>lintel_edge_insulation_work_m</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Кровля</t>
+          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ПВХ мембрана Logicroof V-GR 1,5 мм (эксплуатируемая кровля)</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>рул</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" t="n">
-        <v>1146.91</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>111.76</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: такая же цена, как у обычной V-RP мембраны (1146.91 руб./рул, прайс Елены лист 'Утеплителипленкимастика (Олег)' строка 29 - в прайсе V-GR и V-RP указаны с одинаковой ценой). Пользователь вписывал эту цену вручную в гугл-таблицу 2026-08-06 после того, как для одного из реальных проектов впервые понадобилась V-GR (эксплуатируемая зона кровли) - перенесено в реестр, чтобы не терялось при пересборке.</t>
+          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_logicroof_vgr_1_5mm_gray_roll</t>
+          <t>roof_geotextile_technonikol_prof_300_m2</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
+          <t>Воронка кровельная внутренняя с обогревом (материал)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>6610</v>
+        <v>5000</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Добавлено 2026-08-06: материалы не читаются автоматическим скриптом (только первый лист 'Прайс по видам работ', лист с материалами 'Утеплителипленкимастика (Олег)' сюда не входит) - цена 5000 руб./шт взята оттуда напрямую, строка 32 ('Воронка кровельная (с обжимным мет. фланцем с обогревом 110х450мм)'). До этой правки код случайно получал ту же цену через устаревшее (неверное) сопоставление с работой монтажа - см. исправление в MANUAL_WORK_PRICE_CODES выше. Цена совпала случайно (обе 5000), поэтому баг был незаметен.</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>roof_internal_drain_with_heating_item</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
+          <t>ПВХ мембрана Logicroof V-GR 1,5 мм (эксплуатируемая кровля)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>рул</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
       </c>
       <c r="E185" t="n">
-        <v>450</v>
+        <v>1146.91</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Добавлено 2026-08-06: такая же цена, как у обычной V-RP мембраны (1146.91 руб./рул, прайс Елены лист 'Утеплителипленкимастика (Олег)' строка 29 - в прайсе V-GR и V-RP указаны с одинаковой ценой). Пользователь вписывал эту цену вручную в гугл-таблицу 2026-08-06 после того, как для одного из реальных проектов впервые понадобилась V-GR (эксплуатируемая зона кровли) - перенесено в реестр, чтобы не терялось при пересборке.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>roof_pvc_membrane_logicroof_vgr_1_5mm_gray_roll</t>
         </is>
       </c>
     </row>
@@ -6405,16 +6431,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
+          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>59.55</v>
+        <v>6610</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -6430,7 +6456,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
+          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6439,11 +6465,11 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6001.23</v>
+        <v>450</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
@@ -6455,20 +6481,25 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
+          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2060</v>
+        <v>59.55</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
           <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>roof_fiberglass_mat_technonikol_100gr_m2</t>
         </is>
       </c>
     </row>
@@ -6480,20 +6511,20 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
+          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
+        <v>6001.23</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
@@ -6505,25 +6536,25 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
+          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>7377.89</v>
+        <v>2388</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>roof_eps100_technonikol_carbon_eco_m3</t>
+          <t>roof_screed_board_cementitious_particle_board_12mm</t>
         </is>
       </c>
     </row>
@@ -6535,25 +6566,20 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
+          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>7155.34</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
+        <v>23.12</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>roof_eps50_technonikol_carbon_eco_m3</t>
+          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6591,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6574,7 +6600,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>9888.67</v>
+        <v>7377.89</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -6583,7 +6609,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_a_m3</t>
+          <t>roof_eps100_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6621,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6604,7 +6630,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>9888.67</v>
+        <v>7155.34</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -6613,7 +6639,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_b_m3</t>
+          <t>roof_eps50_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6651,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6643,7 +6669,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>roof_eps_slope_4_2_plate_j_m3</t>
+          <t>roof_eps_slope_2_1_plate_a_m3</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6681,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6673,7 +6699,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>roof_eps_slope_4_2_plate_k_m3</t>
+          <t>roof_eps_slope_2_1_plate_b_m3</t>
         </is>
       </c>
     </row>
@@ -6685,16 +6711,16 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>57.56</v>
+        <v>9888.67</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -6703,7 +6729,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>roof_geotextile_technonikol_prof_150_m2</t>
+          <t>roof_eps_slope_4_2_plate_j_m3</t>
         </is>
       </c>
     </row>
@@ -6715,16 +6741,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Рейка прижимная, 2 м</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>пог. м</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>90</v>
+        <v>9888.67</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -6733,7 +6759,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>roof_aluminum_pressure_rail_m</t>
+          <t>roof_eps_slope_4_2_plate_k_m3</t>
         </is>
       </c>
     </row>
@@ -6745,16 +6771,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Рейка краевая, 2 м</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>пог. м</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>95</v>
+        <v>57.56</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -6763,7 +6789,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>roof_aluminum_edge_rail_m</t>
+          <t>roof_geotextile_technonikol_prof_150_m2</t>
         </is>
       </c>
     </row>
@@ -6775,16 +6801,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
+          <t>Рейка прижимная, 2 м</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>пог. м</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1146.91</v>
+        <v>90</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -6793,7 +6819,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
+          <t>roof_aluminum_pressure_rail_m</t>
         </is>
       </c>
     </row>
@@ -6805,96 +6831,80 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Аэратор кровельный PVC, А75х375</t>
+          <t>Рейка краевая, 2 м</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>пог. м</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>587</v>
+        <v>95</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>roof_pvc_aerator_75x375_item</t>
+          <t>roof_aluminum_edge_rail_m</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
+          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>1</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="E201" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+        <v>1146.91</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>roof_crane_lifting_shift</t>
+          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
+          <t>Аэратор кровельный PVC, А75х375</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E202" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.</t>
-        </is>
+        <v>587</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>roof_internal_drain_pvc_110mm_m</t>
+          <t>roof_pvc_aerator_75x375_item</t>
         </is>
       </c>
     </row>
@@ -6906,33 +6916,33 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Пароизоляция основания плёнкой ПВХ</t>
+          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D203" t="n">
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>77</v>
+        <v>15000</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>roof_vapor_barrier_installation_work_m2</t>
+          <t>roof_crane_lifting_shift</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6954,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Монтаж примыкания кровли из ПВХ мембраны</t>
+          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6956,21 +6966,21 @@
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-02 по сверке эталонных смет: общее линейное примыкание кровли к парапетам/стенам/ВК считается в м.п.; отдельное примыкание к вентшахтам в шт остается optional legacy.</t>
+          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_abutment_work_m</t>
+          <t>roof_internal_drain_pvc_110mm_m</t>
         </is>
       </c>
     </row>
@@ -6982,33 +6992,33 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Монтаж примыкания к вентшахтам</t>
+          <t>Пароизоляция основания плёнкой ПВХ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D205" t="n">
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>5000</v>
+        <v>77</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>roof_vent_shaft_abutment_installation_item</t>
+          <t>roof_vapor_barrier_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -7020,33 +7030,33 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
+          <t>Монтаж примыкания кровли из ПВХ мембраны</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D206" t="n">
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Добавлено 2026-08-02 по сверке эталонных смет: общее линейное примыкание кровли к парапетам/стенам/ВК считается в м.п.; отдельное примыкание к вентшахтам в шт остается optional legacy.</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>roof_internal_drain_with_heating_installation_item</t>
+          <t>roof_pvc_membrane_abutment_work_m</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7068,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Установка аэратора кровельного PVC, А75х375</t>
+          <t>Монтаж примыкания к вентшахтам</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7070,33 +7080,33 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>roof_pvc_aerator_75x375_installation_item</t>
+          <t>roof_vent_shaft_abutment_installation_item</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7108,26 +7118,33 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>268.4</v>
-      </c>
-      <c r="F208" s="2" t="n">
-        <v>46146</v>
+        <v>5000</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>roof_internal_drain_with_heating_installation_item</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+          <t>Установка аэратора кровельного PVC, А75х375</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7139,14 +7156,21 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>902.8</v>
-      </c>
-      <c r="F209" s="2" t="n">
-        <v>46146</v>
+        <v>2500</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>roof_pvc_aerator_75x375_installation_item</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7182,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7170,14 +7194,14 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>264</v>
+        <v>268.4</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7213,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7201,14 +7225,14 @@
         <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>672</v>
+        <v>902.8</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7244,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
+          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7232,19 +7256,14 @@
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>512.4</v>
+        <v>264</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>schiedel_vent_channel_2x_36_25_item</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7275,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
+          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7268,19 +7287,14 @@
         <v>1</v>
       </c>
       <c r="E213" t="n">
-        <v>732</v>
+        <v>672</v>
       </c>
       <c r="F213" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>schiedel_vent_channel_3x_52_25_item</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7292,33 +7306,31 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Доставка вентканалов (машина/транспорт, без разгрузки)</t>
+          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D214" t="n">
         <v>1</v>
       </c>
       <c r="E214" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+        <v>512.4</v>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: было ошибочно затёрто на 2500 через устаревшее правило MANUAL_WORK_PRICE_CODES, которое мапило комбинированную строку 'Доставка+разгрузка' (2500) на этот материальный код - двойной счёт с schiedel_delivery_unloading_work. Реальное значение 15000 подтверждено на листе реальной сметы 'АЛ 06.04 КР1,КР2 (ЕЧ) (ЮВ)', строка 235 'Доставка вентканалов': материал=15000, работа=2500 - оба параллельных блока колонок (левый/белый и правый/серый) сходятся на этой цифре, без разночтений.</t>
+          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>schiedel_delivery_truck</t>
+          <t>schiedel_vent_channel_2x_36_25_item</t>
         </is>
       </c>
     </row>
@@ -7330,33 +7342,31 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Доставка вентканалов, разгрузка вручную</t>
+          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D215" t="n">
         <v>1</v>
       </c>
       <c r="E215" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+        <v>732</v>
+      </c>
+      <c r="F215" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: этой строки нет в прайсе Елены отдельно (там доставка+разгрузка одной строкой = 2500) - ставка взята из реальной сметы одного из проектов, где разгрузка вручную идет отдельной строкой от доставки и стабильно равна 2500 руб./маш независимо от цены самой доставки (проверено в 2 разных листах этой сметы: 2500/2500 и 15000/2500). По решению пользователя 2026-08-06 материал и работа считаются раздельно как более универсальный подход, а не совмещенной строкой как в другом реальном проекте.</t>
+          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>schiedel_delivery_unloading_work</t>
+          <t>schiedel_vent_channel_3x_52_25_item</t>
         </is>
       </c>
     </row>
@@ -7368,33 +7378,33 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+          <t>Доставка вентканалов (машина/транспорт, без разгрузки)</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="D216" t="n">
         <v>1</v>
       </c>
       <c r="E216" t="n">
-        <v>268.4</v>
+        <v>15000</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 27. h=330мм, габариты 200х250мм, вес 13кг, 63 шт на поддоне.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: было ошибочно затёрто на 2500 через устаревшее правило MANUAL_WORK_PRICE_CODES, которое мапило комбинированную строку 'Доставка+разгрузка' (2500) на этот материальный код - двойной счёт с schiedel_delivery_unloading_work. Реальное значение 15000 подтверждено на листе реальной сметы 'АЛ 06.04 КР1,КР2 (ЕЧ) (ЮВ)', строка 235 'Доставка вентканалов': материал=15000, работа=2500 - оба параллельных блока колонок (левый/белый и правый/серый) сходятся на этой цифре, без разночтений.</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_1x_item</t>
+          <t>schiedel_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -7406,33 +7416,33 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+          <t>Доставка вентканалов, разгрузка вручную</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="D217" t="n">
         <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>902.8</v>
+        <v>2500</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 30. h=330мм, габариты 500х360мм, вес 38кг, 16 шт на поддоне.</t>
+          <t>Добавлено 2026-08-06: этой строки нет в прайсе Елены отдельно (там доставка+разгрузка одной строкой = 2500) - ставка взята из реальной сметы одного из проектов, где разгрузка вручную идет отдельной строкой от доставки и стабильно равна 2500 руб./маш независимо от цены самой доставки (проверено в 2 разных листах этой сметы: 2500/2500 и 15000/2500). По решению пользователя 2026-08-06 материал и работа считаются раздельно как более универсальный подход, а не совмещенной строкой как в другом реальном проекте.</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_4x_item</t>
+          <t>schiedel_delivery_unloading_work</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7454,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Вентканал CVENT 26х26 (канал + вентблок-спутник)</t>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7456,94 +7466,97 @@
         <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>2663.2</v>
+        <v>268.4</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: было два кандидата на листе 'Блокпаротермшидель (Алексей)' прайса Елены - строка 33 'Вентблок CVENT 26*26 со спутником, 0.327' = 961.2 руб./шт и строка 34 'Вентиляционный канал Schiedel CVENT 500Х360Х327 26Х26' = 1702 руб./шт. Пользователь подтвердила 2026-08-06: это не два кандидата на один и тот же продукт, а два РАЗНЫХ компонента одного полного CVENT-узла (канал-модуль + его блок-спутник той же глубины 327мм) - берутся оба, цена = сумма 961.2 + 1702 = 2663.2 руб./шт. Калькулятор (CHANNEL_TYPE_SPECS['cvent'] в schiedel_vent_channels_calculator/calculator.py) хранит только ОДНУ цену на product_type=cvent, как и для 1x/2x/3x/4x - поэтому сумма зашита здесь одним числом, а не как два отдельных price_code; calculator.py не менялся. CVENT остаётся редкой строкой (Elena 2026-07-30: 'бывает достаточно редко'), ни один реальный проект её пока не использовал.</t>
+          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 27. h=330мм, габариты 200х250мм, вес 13кг, 63 шт на поддоне.</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_cvent_item</t>
+          <t>schiedel_vent_channel_1x_item</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Schiedel</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Доставка вентканалов/ разгрузка в ручную на объекте</t>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D219" t="n">
         <v>1</v>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>2 500</t>
-        </is>
+      <c r="E219" t="n">
+        <v>902.8</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
+          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 30. h=330мм, габариты 500х360мм, вес 38кг, 16 шт на поддоне.</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_4x_item</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Schiedel</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой более 250мм)</t>
+          <t>Вентканал CVENT 26х26 (канал + вентблок-спутник)</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D220" t="n">
         <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>25000</v>
+        <v>2663.2</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Источник: первый лист прайса Елены (price_registry_elena_2026-07-28.xlsx), строка 29. Ранее исключалась по решению Елены от 2026-07-30 (единая ставка по м.п.); решение пересмотрено 2026-08-09 (подтверждено на 2 реальных проектах, балки делятся по высоте) и повторно подтверждено 2026-08-15 - балки делим, эта строка снова активна. price_code: beam_concrete_placing_work_m3.</t>
+          <t>Добавлено 2026-08-06: было два кандидата на листе 'Блокпаротермшидель (Алексей)' прайса Елены - строка 33 'Вентблок CVENT 26*26 со спутником, 0.327' = 961.2 руб./шт и строка 34 'Вентиляционный канал Schiedel CVENT 500Х360Х327 26Х26' = 1702 руб./шт. Пользователь подтвердила 2026-08-06: это не два кандидата на один и тот же продукт, а два РАЗНЫХ компонента одного полного CVENT-узла (канал-модуль + его блок-спутник той же глубины 327мм) - берутся оба, цена = сумма 961.2 + 1702 = 2663.2 руб./шт. Калькулятор (CHANNEL_TYPE_SPECS['cvent'] в schiedel_vent_channels_calculator/calculator.py) хранит только ОДНУ цену на product_type=cvent, как и для 1x/2x/3x/4x - поэтому сумма зашита здесь одним числом, а не как два отдельных price_code; calculator.py не менялся. CVENT остаётся редкой строкой (Elena 2026-07-30: 'бывает достаточно редко'), ни один реальный проект её пока не использовал.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>beam_concrete_placing_work_m3</t>
+          <t>schiedel_vent_channel_cvent_item</t>
         </is>
       </c>
     </row>
@@ -7555,31 +7568,66 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Гидроизоляция отсечная, битумсодержащая типа ТЕХНОНИКОЛЬ master, материал</t>
+          <t>Доставка вентканалов/ разгрузка в ручную на объекте</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2 500</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Материалы</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Гидроизоляция отсечная, битумсодержащая типа ТЕХНОНИКОЛЬ master (материал, СТО 72746455-3.1.23-2017)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
           <t>м2</t>
         </is>
       </c>
-      <c r="D221" t="n">
-        <v>1</v>
-      </c>
-      <c r="E221" t="n">
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="n">
         <v>250</v>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>В сыром прайс-листе Елены (ни "Прайс по видам работ", ни "Утеплителипленкимастика") этого материала нет - только работа (100р/м2) там есть отдельно. Цена 250р/м2 взята напрямую из серых/внутренних колонок 2 реальных сданных смет: ТРЦ ("НС 29.06.26", строка 88, 28.4075м2) и АРК ("ЕЧ точный 27.04.26", строка 140, 35.3855м2 + строка 322 перегородки 7.83м2) - оба проекта дают идентичную цифру 250р/м2. ЮСВ не даёт отдельной цифры материала в имеющемся файле (только 100р/м2 работы, без материального разреза) - не противоречит, просто нет данных. Материал по PDF во всех 3 проектах: Гидроизоляция отсечная, битумсодержащая типа ТЕХНОНИКОЛЬ master, СТО 72746455-3.1.23-2017.</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>В сыром прайсе Елены отсутствует (проверены оба листа: Прайс по видам работ, Утеплителипленкимастика). Подтверждено идентично на 2 реальных сметах (ТРЦ и АРК, серые/внутренние колонки): материал 250р/м2, работа 100р/м2 (работа уже есть отдельным кодом cutoff_waterproofing_under_blocks_m2). См. reports/trc_vs_original_comparison/04_load_bearing_walls_lintels.md.</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
         <is>
           <t>cutoff_waterproofing_material_m2</t>
         </is>
